--- a/data7.xlsx
+++ b/data7.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asarantsev\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asarantsev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125C5C69-31D8-4D5E-81C6-C32554563FFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2542281-4F04-4B18-BB50-3A10D90D6E27}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17505" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -113,12 +113,6 @@
     <t>January</t>
   </si>
   <si>
-    <t>Dividends per share of the Standard &amp; Poor Composite Index, annual 1871-2023</t>
-  </si>
-  <si>
-    <t>Earnings per share of the Standard &amp; Poor Composite Index, annual 1871-2023</t>
-  </si>
-  <si>
     <t>CPI for all urban consumers: All items in US City Average, FRED series CPIAUCNS</t>
   </si>
   <si>
@@ -146,28 +140,34 @@
     <t>2012- Jan 2021</t>
   </si>
   <si>
-    <t>1919-2025</t>
-  </si>
-  <si>
-    <t>Average monthly close, Standard &amp; Poor Composite Index, January 1871-January 2025</t>
-  </si>
-  <si>
-    <t>Stock and bond markets 1871-2025 in the United States of America</t>
-  </si>
-  <si>
-    <t>1954-2025</t>
-  </si>
-  <si>
     <t>Jul 2021-2025</t>
   </si>
   <si>
-    <t>1913-2025</t>
+    <t>Dividends per share of the Standard &amp; Poor Composite Index, annual 1871-2025</t>
   </si>
   <si>
-    <t>Collected January 22, 2026</t>
+    <t>Earnings per share of the Standard &amp; Poor Composite Index, annual 1871-2025</t>
   </si>
   <si>
-    <t>1957-2025: Standard &amp; Poor 500</t>
+    <t>Average monthly close, Standard &amp; Poor Composite Index, January 1871-January 2026</t>
+  </si>
+  <si>
+    <t>1913-2026</t>
+  </si>
+  <si>
+    <t>1919-2026</t>
+  </si>
+  <si>
+    <t>1954-2026</t>
+  </si>
+  <si>
+    <t>Collected May 7, 2026</t>
+  </si>
+  <si>
+    <t>1957-2026: Standard &amp; Poor 500</t>
+  </si>
+  <si>
+    <t>Stock and bond markets 1871-2026 in the United States of America</t>
   </si>
 </sst>
 </file>
@@ -643,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J156"/>
+  <dimension ref="A1:J157"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="2" bestFit="1" customWidth="1"/>
@@ -4824,7 +4824,10 @@
         <v>2025</v>
       </c>
       <c r="B156" s="5">
-        <v>78.92</v>
+        <v>79.52</v>
+      </c>
+      <c r="C156" s="5">
+        <v>253.11</v>
       </c>
       <c r="D156" s="5">
         <v>5979.52</v>
@@ -4840,6 +4843,23 @@
       </c>
       <c r="H156" s="15">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D157" s="5">
+        <v>6929.12</v>
+      </c>
+      <c r="E157" s="3">
+        <v>325.25</v>
+      </c>
+      <c r="F157" s="2">
+        <v>5.34</v>
+      </c>
+      <c r="G157" s="9">
+        <v>4.21</v>
       </c>
     </row>
   </sheetData>
@@ -4864,7 +4884,7 @@
     </row>
     <row r="2" spans="1:2" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -4884,7 +4904,7 @@
     </row>
     <row r="6" spans="1:2" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -4902,7 +4922,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="8" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -4910,7 +4930,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -4941,7 +4961,7 @@
     </row>
     <row r="15" spans="1:2" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>13</v>
@@ -4965,7 +4985,7 @@
     </row>
     <row r="18" spans="1:2" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>15</v>
@@ -4984,39 +5004,39 @@
         <v>9</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:2" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:2" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="18" x14ac:dyDescent="0.25">
@@ -5029,10 +5049,10 @@
     </row>
     <row r="26" spans="1:2" ht="18" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:2" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.25">
@@ -5049,7 +5069,7 @@
     </row>
     <row r="29" spans="1:2" ht="18" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
